--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>RK09K1130A5R</t>
+          <t>RK09K1130A70</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>C209779</t>
+          <t>C351173</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>GENUINE ALPS B10k linear snap-in, 3.4k stock</t>
+          <t>GENUINE ALPS B10k linear snap-in, 30mm shaft (was A5R/20mm - fixes knob protrusion, same footprint), JLC 7.7k stock</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>RK09K1130A5R</t>
+          <t>RK09K1130A70</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>C209779</t>
+          <t>C351173</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>GENUINE ALPS B10k linear snap-in, 3.4k stock</t>
+          <t>GENUINE ALPS B10k linear snap-in, 30mm shaft (was A5R/20mm - fixes knob protrusion, same footprint), JLC 7.7k stock</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>RK09K1130A5R</t>
+          <t>RK09K1130A70</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>C209779</t>
+          <t>C351173</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>GENUINE ALPS B10k linear snap-in, 3.4k stock</t>
+          <t>GENUINE ALPS B10k linear snap-in, 30mm shaft (was A5R/20mm - fixes knob protrusion, same footprint), JLC 7.7k stock</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>RK09K1130A5R</t>
+          <t>RK09K1130A70</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>C209779</t>
+          <t>C351173</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>GENUINE ALPS B10k linear snap-in, 3.4k stock</t>
+          <t>GENUINE ALPS B10k linear snap-in, 30mm shaft (was A5R/20mm - fixes knob protrusion, same footprint), JLC 7.7k stock</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>RK09K1130A5R</t>
+          <t>RK09K1130A70</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>C209779</t>
+          <t>C351173</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>GENUINE ALPS B10k linear snap-in, 3.4k stock</t>
+          <t>GENUINE ALPS B10k linear snap-in, 30mm shaft (was A5R/20mm - fixes knob protrusion, same footprint), JLC 7.7k stock</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>RK09K1130A5R</t>
+          <t>RK09K1130A70</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>C209779</t>
+          <t>C351173</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>GENUINE ALPS B10k linear snap-in, 3.4k stock</t>
+          <t>GENUINE ALPS B10k linear snap-in, 30mm shaft (was A5R/20mm - fixes knob protrusion, same footprint), JLC 7.7k stock</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Pots: RK09K1130A5R C209779 genuine ALPS. Jacks: C309273 / C5146694 / C319095 all verified.</t>
+          <t xml:space="preserve">  Pots: RK09K1130A70 C351173 genuine ALPS (30mm shaft - fixes knob protrusion, drop-in same footprint). Jacks: C309273 / C5146694 / C319095 all verified.</t>
         </is>
       </c>
     </row>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>C2513</t>
+          <t>C173431</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>C176862</t>
+          <t>C173405</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN8040_8x8.15mm</t>
+          <t>L_12x12mm_H8mm</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 470u</t>
+          <t>RVT1V471M1010</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C3350</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 10u</t>
+          <t>RVT1V100M0405</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C72485</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 4.7u</t>
+          <t>RVT1V4R7M0405</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C72511</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 22u</t>
+          <t>RVT1V220M0505</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C72504</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 47u</t>
+          <t>RVT1V470M0605</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C72522</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 220u/35V</t>
+          <t>RVT1V221M0810</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C3340</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MLCC 100n</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MLCC 10n</t>
+          <t>GRM1885C1H103JA01D</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C85973</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MLCC 1n</t>
+          <t>CL10C102JB8NNNC</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C163508</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MLCC 1u</t>
+          <t>CL10B105KB8NQNC</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C5199872</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MLCC 220n</t>
+          <t>TCC0603X7R224K500CT</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C344195</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MLCC 220p</t>
+          <t>CL10C221JB8NNNC</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C27675</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MLCC 3.9n</t>
+          <t>GRM1885C1H392JA01D</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C415537</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MLCC 3n3</t>
+          <t>0603N332J500CT</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C152910</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MLCC 47n</t>
+          <t>CL10B473KB8NNNC</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C1622</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MLCC 56n</t>
+          <t>CC0603KRX7R9BB563</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C282072</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>MLCC DNP-LFIL</t>
+          <t>DNP - not fitted</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>MLCC DNP-OFIL</t>
+          <t>DNP - not fitted</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MLCC 22u</t>
+          <t>CL21A226MAQNNNE</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C45783</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MLCC 10u/50V X7R</t>
+          <t>CL31B106KBHNNNE</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C89632</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2.54 pin header 2x8</t>
+          <t>PM254V-12-16-H85</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C46595985</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>ferrite bead 1206 600R@100MHz 3A</t>
+          <t>HCB3216KF-601T30</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C357023</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 0R</t>
+          <t>0603WAF0000T5E</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C21189</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 100R</t>
+          <t>0603WAF1000T5E</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22775</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 100k</t>
+          <t>0603WAF1003T5E</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25803</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 10k</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 10k</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 147k</t>
+          <t>0603WAF1473T5E</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22878</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 150k</t>
+          <t>0603WAF1503T5E</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22807</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 15k</t>
+          <t>0603WAF1502T5E</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22809</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 18k</t>
+          <t>0603WAF1802T5E</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25810</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 1M</t>
+          <t>0603WAF1004T5E</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22935</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 1k</t>
+          <t>0603WAF1001T5E</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C21190</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 1k</t>
+          <t>0603WAF1001T5E</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C21190</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 2.2M</t>
+          <t>0603WAF2204T5E</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22938</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 2.2k</t>
+          <t>0603WAF2201T5E</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C4190</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 200k</t>
+          <t>0603WAF2003T5E</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25811</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 20k</t>
+          <t>0603WAF2002T5E</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C4184</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 220k</t>
+          <t>0603WAF2203T5E</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22961</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 22k</t>
+          <t>0603WAF2202T5E</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C31850</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 24k9</t>
+          <t>0603WAF2492T5E</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25962</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 3.3k</t>
+          <t>0603WAF3301T5E</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22978</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 3.6k</t>
+          <t>0603WAF3601T5E</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C22980</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 3.9k</t>
+          <t>0603WAF3901T5E</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23018</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 330k</t>
+          <t>0603WAF3303T5E</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23137</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 33k</t>
+          <t>0603WAF3302T5E</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C4216</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 36k</t>
+          <t>0603WAF3602T5E</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23147</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 39k</t>
+          <t>0603WAF3902T5E</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23153</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 4.3k</t>
+          <t>0603WAF4301T5E</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23159</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 4.7k</t>
+          <t>0603WAF4701T5E</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23162</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 40k2</t>
+          <t>0603WAF4022T5E</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C12447</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 43k</t>
+          <t>0603WAF4302T5E</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23172</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 470R</t>
+          <t>0603WAF4700T5E</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23179</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 470k</t>
+          <t>0603WAF4703T5E</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23178</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 47k</t>
+          <t>0603WAF4702T5E</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C25819</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 51k</t>
+          <t>0603WAF5102T5E</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23196</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 51k</t>
+          <t>0603WAF5102T5E</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23196</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 6.8k</t>
+          <t>0603WAF6801T5E</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23212</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 680</t>
+          <t>0603WAF6800T5E</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23228</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 7k68</t>
+          <t>0603WAF7681T5E</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C23102</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>0603 1% resistor 845R</t>
+          <t>FRC0603F8450TS</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C2933262</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>SMD alu electrolytic 100u</t>
+          <t>RVE100UF35V67RV0072</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C2836437</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MLCC 100n</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2.54 socket/header 2x8</t>
+          <t>PZ254V-12-16P</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>C492425</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>SSWFS-S01-AC09-HWH</t>
+          <t>SSWFS-S01-AC09-HWH (PC-pin) or Amplified Parts P-H604 equivalent</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -5268,15 +5268,19 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>SSWFS-S01-AC09-HWH</t>
+          <t>CUSTOMER SUPPLIED</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>PC-pin soft stomp; Marketplace - confirm PCBWay can buy; fallback AC05 lug + wires</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+          <t>DO NOT SOURCE - no fab-side distributor stocks this class of part (Digi-Key Marketplace only; Mouser none; JLCPCB has no foot-switch category). Commodity pedal part: Love My Switches PCB-mount \.99, Amplified Parts P-H604 dimensions match (12mm x 1mm bushing, 14.3 long, body 25.3 x 12.6). Fitted by Jason at final assembly. PC-pin variant chosen 2026-08-02 - no board cutouts needed.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
